--- a/output/東北_上下水道経営戦略_改訂時期一覧.xlsx
+++ b/output/東北_上下水道経営戦略_改訂時期一覧.xlsx
@@ -107,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -141,9 +141,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -226,8 +223,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T2344" displayName="T2344" ref="A2:O34" headerRowCount="1">
-  <autoFilter ref="A2:O34"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T20296" displayName="T20296" ref="A2:O36" headerRowCount="1">
+  <autoFilter ref="A2:O36"/>
   <tableColumns count="15">
     <tableColumn id="1" name="振興局"/>
     <tableColumn id="2" name="自治体"/>
@@ -250,8 +247,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T56999" displayName="T56999" ref="A2:O5" headerRowCount="1">
-  <autoFilter ref="A2:O5"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T95258" displayName="T95258" ref="A2:O6" headerRowCount="1">
+  <autoFilter ref="A2:O6"/>
   <tableColumns count="15">
     <tableColumn id="1" name="振興局"/>
     <tableColumn id="2" name="自治体"/>
@@ -274,7 +271,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T68584" displayName="T68584" ref="A2:O7" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T65305" displayName="T65305" ref="A2:O7" headerRowCount="1">
   <autoFilter ref="A2:O7"/>
   <tableColumns count="15">
     <tableColumn id="1" name="振興局"/>
@@ -298,7 +295,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="T31505" displayName="T31505" ref="A2:O15" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="T66183" displayName="T66183" ref="A2:O15" headerRowCount="1">
   <autoFilter ref="A2:O15"/>
   <tableColumns count="15">
     <tableColumn id="1" name="振興局"/>
@@ -322,7 +319,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="T7389" displayName="T7389" ref="A2:O7" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="T94539" displayName="T94539" ref="A2:O7" headerRowCount="1">
   <autoFilter ref="A2:O7"/>
   <tableColumns count="15">
     <tableColumn id="1" name="振興局"/>
@@ -346,8 +343,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="T11350" displayName="T11350" ref="A2:O12" headerRowCount="1">
-  <autoFilter ref="A2:O12"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="T16283" displayName="T16283" ref="A2:O13" headerRowCount="1">
+  <autoFilter ref="A2:O13"/>
   <tableColumns count="15">
     <tableColumn id="1" name="振興局"/>
     <tableColumn id="2" name="自治体"/>
@@ -370,7 +367,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="T7057" displayName="T7057" ref="A2:O5" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="T50427" displayName="T50427" ref="A2:O5" headerRowCount="1">
   <autoFilter ref="A2:O5"/>
   <tableColumns count="15">
     <tableColumn id="1" name="振興局"/>
@@ -832,7 +829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O34"/>
+  <dimension ref="A1:O36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1043,12 +1040,12 @@
       </c>
       <c r="N4" s="6" t="inlineStr">
         <is>
-          <t>八戸市の水道は八戸圏域水道企業団が運営。計画期間は要確認</t>
+          <t>検索では計画期間を特定できず。企業団経営企画課への個別確認が必要（八戸市・三戸町等の構成団体）</t>
         </is>
       </c>
       <c r="O4" s="6" t="inlineStr">
         <is>
-          <t>https://www.city.hachinohe.aomori.jp/soshikikarasagasu/gesuidogyomuka/2621.html</t>
+          <t>https://www.water-supply.hachinohe.aomori.jp/</t>
         </is>
       </c>
     </row>
@@ -1353,43 +1350,65 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>水道・下水道</t>
+          <t>下水道</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>一関市経営戦略</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr"/>
-      <c r="F9" s="5" t="inlineStr"/>
+          <t>一関市下水道事業経営戦略</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>平成28年度(2016)</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>令和4年度(2022)</t>
+        </is>
+      </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr"/>
-      <c r="I9" s="5" t="inlineStr"/>
-      <c r="J9" s="5" t="inlineStr"/>
-      <c r="K9" s="5" t="inlineStr"/>
-      <c r="L9" s="8" t="inlineStr">
-        <is>
-          <t>－：情報未確認</t>
+          <t>平成29年度(2017)～令和8年度(2026)</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>今年度末満了（2027年3月）</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>4年経過（翌年度に5年）</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>今年度末満了／翌年度5年</t>
+        </is>
+      </c>
+      <c r="L9" s="9" t="inlineStr">
+        <is>
+          <t>A：改訂着手が必要</t>
         </is>
       </c>
       <c r="M9" s="5" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>中</t>
         </is>
       </c>
       <c r="N9" s="6" t="inlineStr">
         <is>
-          <t>汚水処理施設概成アクションプランはH28-R8年度末。経営戦略の計画期間は要確認</t>
+          <t>平成29年3月策定。令和5年3月版PDFあり（改定）。汚水処理施設整備計画はH29-H38（＝R8年度）。改定後の計画期間は要電話確認</t>
         </is>
       </c>
       <c r="O9" s="6" t="inlineStr">
         <is>
-          <t>https://www.city.ichinoseki.iwate.jp/water/</t>
+          <t>https://www.city.ichinoseki.iwate.jp/uploads/contents/archive_0000000308_00/20230331-110723.pdf</t>
         </is>
       </c>
     </row>
@@ -1401,66 +1420,66 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>北上市</t>
+          <t>一関市</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>下水道（公共・農業集落排水）</t>
+          <t>水道</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>北上市下水道事業経営戦略</t>
+          <t>一関市水道ビジョン・経営戦略</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>平成28年度(2016)</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr"/>
+          <t>令和7年度(2025)</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>令和7年度(2025)</t>
+        </is>
+      </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>平成29年度(2017)～令和8年度(2026)</t>
+          <t>令和8年度(2026)～令和17年度(2035)</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>今年度末満了（2027年3月）</t>
+          <t>満了は令和17年度(2035)末</t>
         </is>
       </c>
       <c r="I10" s="5" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>10年経過（5年超）</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t>今年度末満了／5年超経過</t>
-        </is>
-      </c>
-      <c r="L10" s="9" t="inlineStr">
-        <is>
-          <t>A：改訂着手が必要</t>
+          <t>1年経過</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr"/>
+      <c r="L10" s="7" t="inlineStr">
+        <is>
+          <t>C：翌年度以降に検討</t>
         </is>
       </c>
       <c r="M10" s="5" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="N10" s="6" t="inlineStr">
         <is>
-          <t>平成29年度～令和8年度の10年間→R8年度末満了</t>
+          <t>令和8年度～令和17年度の案をパブリックコメント中＝改定作業中</t>
         </is>
       </c>
       <c r="O10" s="6" t="inlineStr">
         <is>
-          <t>https://www.city.kitakami.iwate.jp/life/kurashi_tetsuduki/jo_gesuido/gesuido/10131.html</t>
+          <t>https://www.city.ichinoseki.iwate.jp/water/</t>
         </is>
       </c>
     </row>
@@ -1472,66 +1491,48 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>北上市</t>
+          <t>一関市</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>下水道（特定公共下水道）</t>
+          <t>水道・下水道</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>北上市特定公共下水道事業経営戦略</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>平成29年度(2017)</t>
-        </is>
-      </c>
+          <t>一関市経営戦略</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr"/>
       <c r="F11" s="5" t="inlineStr"/>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>平成30年度(2018)～令和8年度(2026)</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>今年度末満了（2027年3月）</t>
-        </is>
-      </c>
-      <c r="I11" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="J11" s="5" t="inlineStr">
-        <is>
-          <t>9年経過（5年超）</t>
-        </is>
-      </c>
-      <c r="K11" s="5" t="inlineStr">
-        <is>
-          <t>今年度末満了／5年超経過</t>
-        </is>
-      </c>
-      <c r="L11" s="9" t="inlineStr">
-        <is>
-          <t>A：改訂着手が必要</t>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr"/>
+      <c r="I11" s="5" t="inlineStr"/>
+      <c r="J11" s="5" t="inlineStr"/>
+      <c r="K11" s="5" t="inlineStr"/>
+      <c r="L11" s="8" t="inlineStr">
+        <is>
+          <t>－：情報未確認</t>
         </is>
       </c>
       <c r="M11" s="5" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>低</t>
         </is>
       </c>
       <c r="N11" s="6" t="inlineStr">
         <is>
-          <t>平成30年度～令和8年度の9年間→R8年度末満了</t>
+          <t>汚水処理施設概成アクションプランはH28-R8年度末。経営戦略の計画期間は要確認</t>
         </is>
       </c>
       <c r="O11" s="6" t="inlineStr">
         <is>
-          <t>https://www.city.kitakami.iwate.jp/life/kurashi_tetsuduki/jo_gesuido/gesuido/10131.html</t>
+          <t>https://www.city.ichinoseki.iwate.jp/water/</t>
         </is>
       </c>
     </row>
@@ -1543,51 +1544,51 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>奥州市</t>
+          <t>北上市</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>下水道</t>
+          <t>下水道（公共・農業集落排水）</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>奥州市下水道事業経営戦略</t>
+          <t>北上市下水道事業経営戦略</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>令和6年度(2024)</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>令和6年度(2024)</t>
-        </is>
-      </c>
+          <t>平成28年度(2016)</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr"/>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>令和7年度(2025)～令和16年度(2034)</t>
+          <t>平成29年度(2017)～令和8年度(2026)</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>満了は令和16年度(2034)末</t>
+          <t>今年度末満了（2027年3月）</t>
         </is>
       </c>
       <c r="I12" s="5" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>2年経過</t>
-        </is>
-      </c>
-      <c r="K12" s="5" t="inlineStr"/>
-      <c r="L12" s="7" t="inlineStr">
-        <is>
-          <t>C：翌年度以降に検討</t>
+          <t>10年経過（5年超）</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>今年度末満了／5年超経過</t>
+        </is>
+      </c>
+      <c r="L12" s="9" t="inlineStr">
+        <is>
+          <t>A：改訂着手が必要</t>
         </is>
       </c>
       <c r="M12" s="5" t="inlineStr">
@@ -1597,12 +1598,12 @@
       </c>
       <c r="N12" s="6" t="inlineStr">
         <is>
-          <t>人口減少・物価高騰を踏まえ改定、R7-R16</t>
+          <t>平成29年度～令和8年度の10年間→R8年度末満了</t>
         </is>
       </c>
       <c r="O12" s="6" t="inlineStr">
         <is>
-          <t>https://www.city.oshu.iwate.jp/suido/jigyou/jigyougaiyou/4562.html</t>
+          <t>https://www.city.kitakami.iwate.jp/life/kurashi_tetsuduki/jo_gesuido/gesuido/10131.html</t>
         </is>
       </c>
     </row>
@@ -1614,51 +1615,51 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>奥州市</t>
+          <t>北上市</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>水道</t>
+          <t>下水道（特定公共下水道）</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>奥州市水道事業経営戦略</t>
+          <t>北上市特定公共下水道事業経営戦略</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>令和7年度(2025)</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>令和7年度(2025)</t>
-        </is>
-      </c>
+          <t>平成29年度(2017)</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr"/>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>令和8年度(2026)～令和17年度(2035)</t>
+          <t>平成30年度(2018)～令和8年度(2026)</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>満了は令和17年度(2035)末</t>
+          <t>今年度末満了（2027年3月）</t>
         </is>
       </c>
       <c r="I13" s="5" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>1年経過</t>
-        </is>
-      </c>
-      <c r="K13" s="5" t="inlineStr"/>
-      <c r="L13" s="7" t="inlineStr">
-        <is>
-          <t>C：翌年度以降に検討</t>
+          <t>9年経過（5年超）</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>今年度末満了／5年超経過</t>
+        </is>
+      </c>
+      <c r="L13" s="9" t="inlineStr">
+        <is>
+          <t>A：改訂着手が必要</t>
         </is>
       </c>
       <c r="M13" s="5" t="inlineStr">
@@ -1668,12 +1669,12 @@
       </c>
       <c r="N13" s="6" t="inlineStr">
         <is>
-          <t>総務省の要請に基づき改定、R8-R17</t>
+          <t>平成30年度～令和8年度の9年間→R8年度末満了</t>
         </is>
       </c>
       <c r="O13" s="6" t="inlineStr">
         <is>
-          <t>https://www.city.oshu.iwate.jp/suido/jigyou/jigyougaiyou/3970.html</t>
+          <t>https://www.city.kitakami.iwate.jp/life/kurashi_tetsuduki/jo_gesuido/gesuido/10131.html</t>
         </is>
       </c>
     </row>
@@ -1685,7 +1686,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>盛岡市</t>
+          <t>奥州市</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -1695,60 +1696,56 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>盛岡市下水道事業中長期経営計画</t>
+          <t>奥州市下水道事業経営戦略</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>平成26年度(2014)</t>
+          <t>令和6年度(2024)</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>平成28年度(2016)</t>
+          <t>令和6年度(2024)</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>平成27年度(2015)～令和6年度(2024)</t>
+          <t>令和7年度(2025)～令和16年度(2034)</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>既に満了（令和6年度(2024)末）</t>
+          <t>満了は令和16年度(2034)末</t>
         </is>
       </c>
       <c r="I14" s="5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>10年経過（5年超）</t>
-        </is>
-      </c>
-      <c r="K14" s="5" t="inlineStr">
-        <is>
-          <t>期間満了済／5年超経過</t>
-        </is>
-      </c>
-      <c r="L14" s="9" t="inlineStr">
-        <is>
-          <t>A：改訂着手が必要</t>
+          <t>2年経過</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr"/>
+      <c r="L14" s="7" t="inlineStr">
+        <is>
+          <t>C：翌年度以降に検討</t>
         </is>
       </c>
       <c r="M14" s="5" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="N14" s="6" t="inlineStr">
         <is>
-          <t>平成27年3月策定（H27-H36＝令和6年度）、平成29年3月改訂→R6年度末で満了。別途「下水道事業中期経営計画」あり、最新版は要確認</t>
+          <t>人口減少・物価高騰を踏まえ改定、R7-R16</t>
         </is>
       </c>
       <c r="O14" s="6" t="inlineStr">
         <is>
-          <t>https://www.morioka-water.jp/about/ge_plan_27-36.html</t>
+          <t>https://www.city.oshu.iwate.jp/suido/jigyou/jigyougaiyou/4562.html</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1757,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>盛岡市</t>
+          <t>奥州市</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -1770,41 +1767,41 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>第三次盛岡市水道事業基本計画（もりおか水道ビジョン）＝経営戦略</t>
+          <t>奥州市水道事業経営戦略</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>平成26年度(2014)</t>
+          <t>令和7年度(2025)</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>令和3年度(2021)</t>
+          <t>令和7年度(2025)</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr"/>
+          <t>令和8年度(2026)～令和17年度(2035)</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>満了は令和17年度(2035)末</t>
+        </is>
+      </c>
       <c r="I15" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>5年経過</t>
-        </is>
-      </c>
-      <c r="K15" s="5" t="inlineStr">
-        <is>
-          <t>5年経過</t>
-        </is>
-      </c>
-      <c r="L15" s="10" t="inlineStr">
-        <is>
-          <t>B：来年度改訂の対象</t>
+          <t>1年経過</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr"/>
+      <c r="L15" s="7" t="inlineStr">
+        <is>
+          <t>C：翌年度以降に検討</t>
         </is>
       </c>
       <c r="M15" s="5" t="inlineStr">
@@ -1814,12 +1811,12 @@
       </c>
       <c r="N15" s="6" t="inlineStr">
         <is>
-          <t>平成27年3月策定→令和3年9月改訂。経営戦略として位置付け。改訂から5年経過</t>
+          <t>総務省の要請に基づき改定、R8-R17</t>
         </is>
       </c>
       <c r="O15" s="6" t="inlineStr">
         <is>
-          <t>https://www.morioka-water.jp/about/kihon_about.html</t>
+          <t>https://www.city.oshu.iwate.jp/suido/jigyou/jigyougaiyou/3970.html</t>
         </is>
       </c>
     </row>
@@ -1831,122 +1828,126 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>花巻市</t>
+          <t>盛岡市</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>下水道（公共・農集排・浄化槽）</t>
+          <t>下水道</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>花巻市下水道事業経営戦略</t>
+          <t>盛岡市下水道事業中長期経営計画</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>令和6年度(2024)</t>
+          <t>平成26年度(2014)</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>令和6年度(2024)</t>
+          <t>平成28年度(2016)</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>令和7年度(2025)～令和16年度(2034)</t>
+          <t>平成27年度(2015)～令和6年度(2024)</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>満了は令和16年度(2034)末</t>
+          <t>既に満了（令和6年度(2024)末）</t>
         </is>
       </c>
       <c r="I16" s="5" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>2年経過</t>
-        </is>
-      </c>
-      <c r="K16" s="5" t="inlineStr"/>
-      <c r="L16" s="7" t="inlineStr">
-        <is>
-          <t>C：翌年度以降に検討</t>
+          <t>10年経過（5年超）</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>期間満了済／5年超経過</t>
+        </is>
+      </c>
+      <c r="L16" s="9" t="inlineStr">
+        <is>
+          <t>A：改訂着手が必要</t>
         </is>
       </c>
       <c r="M16" s="5" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="N16" s="6" t="inlineStr">
         <is>
-          <t>H29.3策定→令和7年3月改定。3事業を統合しR7-R16</t>
+          <t>平成27年3月策定（H27-H36＝令和6年度）、平成29年3月改訂→R6年度末で満了。別途「下水道事業中期経営計画」あり、最新版は要確認</t>
         </is>
       </c>
       <c r="O16" s="6" t="inlineStr">
         <is>
-          <t>https://www.city.hanamaki.iwate.jp/kurashi/suidou/1019833/1001199/1001204.html</t>
+          <t>https://www.morioka-water.jp/about/ge_plan_27-36.html</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>宮城県</t>
+          <t>岩手県</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>仙台市</t>
+          <t>盛岡市</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>下水道</t>
+          <t>水道</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>仙台市下水道事業中期経営計画（後期）</t>
+          <t>第三次盛岡市水道事業基本計画（もりおか水道ビジョン）＝経営戦略</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>令和2年度(2020)</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr"/>
+          <t>平成26年度(2014)</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>令和3年度(2021)</t>
+        </is>
+      </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>令和3年度(2021)～令和7年度(2025)</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>既に満了（令和7年度(2025)末）</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr"/>
       <c r="I17" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>6年経過（5年超）</t>
+          <t>5年経過</t>
         </is>
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>期間満了済／5年超経過</t>
-        </is>
-      </c>
-      <c r="L17" s="9" t="inlineStr">
-        <is>
-          <t>A：改訂着手が必要</t>
+          <t>5年経過</t>
+        </is>
+      </c>
+      <c r="L17" s="10" t="inlineStr">
+        <is>
+          <t>B：来年度改訂の対象</t>
         </is>
       </c>
       <c r="M17" s="5" t="inlineStr">
@@ -1956,39 +1957,39 @@
       </c>
       <c r="N17" s="6" t="inlineStr">
         <is>
-          <t>令和3年3月策定、R3-R7の5年間→R7年度末で満了済。次期計画の策定状況は要確認</t>
+          <t>平成27年3月策定→令和3年9月改訂。経営戦略として位置付け。改訂から5年経過</t>
         </is>
       </c>
       <c r="O17" s="6" t="inlineStr">
         <is>
-          <t>https://www.city.sendai.jp/keesenryaku/kurashi/machi/lifeline/gesuido/gesuido/gaiyo/kee.html</t>
+          <t>https://www.morioka-water.jp/about/kihon_about.html</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>宮城県</t>
+          <t>岩手県</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>仙台市</t>
+          <t>花巻市</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>水道</t>
+          <t>下水道（公共・農集排・浄化槽）</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>仙台市水道事業基本計画／中期経営計画</t>
+          <t>花巻市下水道事業経営戦略</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>令和1年度(2019)</t>
+          <t>令和6年度(2024)</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
@@ -1998,12 +1999,12 @@
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>令和2年度(2020)～令和11年度(2029)</t>
+          <t>令和7年度(2025)～令和16年度(2034)</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>満了は令和11年度(2029)末</t>
+          <t>満了は令和16年度(2034)末</t>
         </is>
       </c>
       <c r="I18" s="5" t="n">
@@ -2022,17 +2023,17 @@
       </c>
       <c r="M18" s="5" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="N18" s="6" t="inlineStr">
         <is>
-          <t>基本計画R2-R11。中期経営計画は前期R2-R6・後期R7-R11の5年区分</t>
+          <t>H29.3策定→令和7年3月改定。3事業を統合しR7-R16</t>
         </is>
       </c>
       <c r="O18" s="6" t="inlineStr">
         <is>
-          <t>http://www.jwwa.or.jp/zenkoku/venue_sendai_02-01.html</t>
+          <t>https://www.city.hanamaki.iwate.jp/kurashi/suidou/1019833/1001199/1001204.html</t>
         </is>
       </c>
     </row>
@@ -2044,7 +2045,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>大崎市</t>
+          <t>仙台市</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -2054,7 +2055,7 @@
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>大崎市下水道事業経営戦略（令和7年3月改定）</t>
+          <t>仙台市下水道事業中期経営計画（後期）</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -2062,33 +2063,33 @@
           <t>令和2年度(2020)</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>令和6年度(2024)</t>
-        </is>
-      </c>
+      <c r="F19" s="5" t="inlineStr"/>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>令和7年度(2025)～令和16年度(2034)</t>
+          <t>令和3年度(2021)～令和7年度(2025)</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>満了は令和16年度(2034)末</t>
+          <t>既に満了（令和7年度(2025)末）</t>
         </is>
       </c>
       <c r="I19" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>2年経過</t>
-        </is>
-      </c>
-      <c r="K19" s="5" t="inlineStr"/>
-      <c r="L19" s="7" t="inlineStr">
-        <is>
-          <t>C：翌年度以降に検討</t>
+          <t>6年経過（5年超）</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>期間満了済／5年超経過</t>
+        </is>
+      </c>
+      <c r="L19" s="9" t="inlineStr">
+        <is>
+          <t>A：改訂着手が必要</t>
         </is>
       </c>
       <c r="M19" s="5" t="inlineStr">
@@ -2098,12 +2099,12 @@
       </c>
       <c r="N19" s="6" t="inlineStr">
         <is>
-          <t>令和3年2月策定→令和7年3月改定で令和7年度からの新たな10年間に</t>
+          <t>令和3年3月策定、R3-R7の5年間→R7年度末で満了済。次期計画の策定状況は要確認</t>
         </is>
       </c>
       <c r="O19" s="6" t="inlineStr">
         <is>
-          <t>https://www.city.osaki.miyagi.jp/shisei/soshikikarasagasu/jogesuidoubu/keieikanrika/3/1/2/7397.html</t>
+          <t>https://www.city.sendai.jp/keesenryaku/kurashi/machi/lifeline/gesuido/gesuido/gaiyo/kee.html</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2116,7 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>大崎市</t>
+          <t>仙台市</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -2125,60 +2126,56 @@
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>大崎市水道事業経営戦略</t>
+          <t>仙台市水道事業基本計画／中期経営計画</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>令和3年度(2021)</t>
+          <t>令和1年度(2019)</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>令和3年度(2021)</t>
+          <t>令和6年度(2024)</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>令和4年度(2022)～令和13年度(2031)</t>
+          <t>令和2年度(2020)～令和11年度(2029)</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>満了は令和13年度(2031)末</t>
+          <t>満了は令和11年度(2029)末</t>
         </is>
       </c>
       <c r="I20" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>5年経過</t>
-        </is>
-      </c>
-      <c r="K20" s="5" t="inlineStr">
-        <is>
-          <t>5年経過</t>
-        </is>
-      </c>
-      <c r="L20" s="10" t="inlineStr">
-        <is>
-          <t>B：来年度改訂の対象</t>
+          <t>2年経過</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="inlineStr"/>
+      <c r="L20" s="7" t="inlineStr">
+        <is>
+          <t>C：翌年度以降に検討</t>
         </is>
       </c>
       <c r="M20" s="5" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="N20" s="6" t="inlineStr">
         <is>
-          <t>平成29年2月策定→令和4年度からの新たな10年間に改定。改定から5年目</t>
+          <t>基本計画R2-R11。中期経営計画は前期R2-R6・後期R7-R11の5年区分</t>
         </is>
       </c>
       <c r="O20" s="6" t="inlineStr">
         <is>
-          <t>https://www.city.osaki.miyagi.jp/shisei/soshikikarasagasu/jogesuidoubu/keieikanrika/3/1/2/3195.html</t>
+          <t>http://www.jwwa.or.jp/zenkoku/venue_sendai_02-01.html</t>
         </is>
       </c>
     </row>
@@ -2190,7 +2187,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>石巻市</t>
+          <t>大崎市</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -2200,82 +2197,78 @@
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>石巻市下水道事業経営戦略（改定版）</t>
+          <t>大崎市下水道事業経営戦略（令和7年3月改定）</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>平成27年度(2015)</t>
+          <t>令和2年度(2020)</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>令和5年度(2023)</t>
+          <t>令和6年度(2024)</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>平成28年度(2016)～令和7年度(2025)</t>
+          <t>令和7年度(2025)～令和16年度(2034)</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>既に満了（令和7年度(2025)末）</t>
+          <t>満了は令和16年度(2034)末</t>
         </is>
       </c>
       <c r="I21" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>3年経過</t>
-        </is>
-      </c>
-      <c r="K21" s="5" t="inlineStr">
-        <is>
-          <t>期間満了済</t>
-        </is>
-      </c>
-      <c r="L21" s="9" t="inlineStr">
-        <is>
-          <t>A：改訂着手が必要</t>
+          <t>2年経過</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr"/>
+      <c r="L21" s="7" t="inlineStr">
+        <is>
+          <t>C：翌年度以降に検討</t>
         </is>
       </c>
       <c r="M21" s="5" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="N21" s="6" t="inlineStr">
         <is>
-          <t>H28.3策定（H28-R7）→R6.2～3にパブコメを経て改定。改定後の計画期間は要確認</t>
+          <t>令和3年2月策定→令和7年3月改定で令和7年度からの新たな10年間に</t>
         </is>
       </c>
       <c r="O21" s="6" t="inlineStr">
         <is>
-          <t>https://www.city.ishinomaki.lg.jp/cont/10505200/20240312085340.html</t>
+          <t>https://www.city.osaki.miyagi.jp/shisei/soshikikarasagasu/jogesuidoubu/keieikanrika/3/1/2/7397.html</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>秋田県</t>
+          <t>宮城県</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>大館市</t>
+          <t>大崎市</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>下水道</t>
+          <t>水道</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>大館市下水道事業経営戦略</t>
+          <t>大崎市水道事業経営戦略</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -2283,7 +2276,11 @@
           <t>令和3年度(2021)</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr"/>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>令和3年度(2021)</t>
+        </is>
+      </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
           <t>令和4年度(2022)～令和13年度(2031)</t>
@@ -2319,83 +2316,87 @@
       </c>
       <c r="N22" s="6" t="inlineStr">
         <is>
-          <t>計画期間R4-R13（収支見通しはR50年度まで推計）。5年毎に見直し</t>
+          <t>平成29年2月策定→令和4年度からの新たな10年間に改定。改定から5年目</t>
         </is>
       </c>
       <c r="O22" s="6" t="inlineStr">
         <is>
-          <t>https://www.city.odate.lg.jp/uploads/public/pages_0000002296_00/大館市下水道事業経営戦略(R4～R13).pdf</t>
+          <t>https://www.city.osaki.miyagi.jp/shisei/soshikikarasagasu/jogesuidoubu/keieikanrika/3/1/2/3195.html</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>秋田県</t>
+          <t>宮城県</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>大館市</t>
+          <t>石巻市</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>工業用水道</t>
+          <t>下水道</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>大館市工業用水道事業経営戦略</t>
+          <t>石巻市下水道事業経営戦略（改定版）</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>令和3年度(2021)</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="inlineStr"/>
+          <t>平成27年度(2015)</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>令和5年度(2023)</t>
+        </is>
+      </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>令和4年度(2022)～令和13年度(2031)</t>
+          <t>平成28年度(2016)～令和7年度(2025)</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>満了は令和13年度(2031)末</t>
+          <t>既に満了（令和7年度(2025)末）</t>
         </is>
       </c>
       <c r="I23" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>5年経過</t>
+          <t>3年経過</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>5年経過</t>
-        </is>
-      </c>
-      <c r="L23" s="10" t="inlineStr">
-        <is>
-          <t>B：来年度改訂の対象</t>
+          <t>期間満了済</t>
+        </is>
+      </c>
+      <c r="L23" s="9" t="inlineStr">
+        <is>
+          <t>A：改訂着手が必要</t>
         </is>
       </c>
       <c r="M23" s="5" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="N23" s="6" t="inlineStr">
         <is>
-          <t>計画期間R4-R13</t>
+          <t>H28.3策定（H28-R7）→R6.2～3にパブコメを経て改定。改定後の計画期間は要確認</t>
         </is>
       </c>
       <c r="O23" s="6" t="inlineStr">
         <is>
-          <t>https://www.city.odate.lg.jp/city/soshiki/suidoukanri/p952</t>
+          <t>https://www.city.ishinomaki.lg.jp/cont/10505200/20240312085340.html</t>
         </is>
       </c>
     </row>
@@ -2412,12 +2413,12 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>水道</t>
+          <t>下水道</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>大館市水道事業経営戦略</t>
+          <t>大館市下水道事業経営戦略</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -2461,12 +2462,12 @@
       </c>
       <c r="N24" s="6" t="inlineStr">
         <is>
-          <t>計画期間R4-R13。5年毎に見直し→R8年度が見直し期</t>
+          <t>計画期間R4-R13（収支見通しはR50年度まで推計）。5年毎に見直し</t>
         </is>
       </c>
       <c r="O24" s="6" t="inlineStr">
         <is>
-          <t>https://www.city.odate.lg.jp/city/soshiki/suidoukanri/p952</t>
+          <t>https://www.city.odate.lg.jp/uploads/public/pages_0000002296_00/大館市下水道事業経営戦略(R4～R13).pdf</t>
         </is>
       </c>
     </row>
@@ -2478,47 +2479,51 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>秋田市</t>
+          <t>大館市</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>水道・下水道・農業集落排水</t>
+          <t>工業用水道</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>秋田市上下水道事業基本計画／各会計の経営戦略</t>
+          <t>大館市工業用水道事業経営戦略</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>令和6年度(2024)</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>令和6年度(2024)</t>
-        </is>
-      </c>
+          <t>令和3年度(2021)</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr"/>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr"/>
+          <t>令和4年度(2022)～令和13年度(2031)</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>満了は令和13年度(2031)末</t>
+        </is>
+      </c>
       <c r="I25" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>2年経過</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="inlineStr"/>
-      <c r="L25" s="7" t="inlineStr">
-        <is>
-          <t>C：翌年度以降に検討</t>
+          <t>5年経過</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>5年経過</t>
+        </is>
+      </c>
+      <c r="L25" s="10" t="inlineStr">
+        <is>
+          <t>B：来年度改訂の対象</t>
         </is>
       </c>
       <c r="M25" s="5" t="inlineStr">
@@ -2528,68 +2533,68 @@
       </c>
       <c r="N25" s="6" t="inlineStr">
         <is>
-          <t>令和7年3月策定。総務省様式で水道・下水道・農集排の会計単位の経営戦略を公表</t>
+          <t>計画期間R4-R13</t>
         </is>
       </c>
       <c r="O25" s="6" t="inlineStr">
         <is>
-          <t>https://www.city.akita.lg.jp/suido/jigyo-shokai/1045766.html</t>
+          <t>https://www.city.odate.lg.jp/city/soshiki/suidoukanri/p952</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>山形県</t>
+          <t>秋田県</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>山形市</t>
+          <t>大館市</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>上下水道（水道・下水道一体）</t>
+          <t>水道</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>山形市上下水道事業基本計画 NEXTビジョン2023</t>
+          <t>大館市水道事業経営戦略</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>令和4年度(2022)</t>
+          <t>令和3年度(2021)</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr"/>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>令和5年度(2023)～令和14年度(2032)</t>
+          <t>令和4年度(2022)～令和13年度(2031)</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>満了は令和14年度(2032)末</t>
+          <t>満了は令和13年度(2031)末</t>
         </is>
       </c>
       <c r="I26" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>4年経過（翌年度に5年）</t>
+          <t>5年経過</t>
         </is>
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>翌年度5年</t>
-        </is>
-      </c>
-      <c r="L26" s="7" t="inlineStr">
-        <is>
-          <t>C：翌年度以降に検討</t>
+          <t>5年経過</t>
+        </is>
+      </c>
+      <c r="L26" s="10" t="inlineStr">
+        <is>
+          <t>B：来年度改訂の対象</t>
         </is>
       </c>
       <c r="M26" s="5" t="inlineStr">
@@ -2599,68 +2604,64 @@
       </c>
       <c r="N26" s="6" t="inlineStr">
         <is>
-          <t>計画期間 令和5年度～令和14年度</t>
+          <t>計画期間R4-R13。5年毎に見直し→R8年度が見直し期</t>
         </is>
       </c>
       <c r="O26" s="6" t="inlineStr">
         <is>
-          <t>https://suidou.yamagata.yamagata.jp/soshiki/3/105858.html</t>
+          <t>https://www.city.odate.lg.jp/city/soshiki/suidoukanri/p952</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>山形県</t>
+          <t>秋田県</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>鶴岡市</t>
+          <t>秋田市</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>下水道</t>
+          <t>水道・下水道・農業集落排水</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>鶴岡市下水道事業経営戦略</t>
+          <t>秋田市上下水道事業基本計画／各会計の経営戦略</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>平成28年度(2016)</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="inlineStr"/>
+          <t>令和6年度(2024)</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>令和6年度(2024)</t>
+        </is>
+      </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>平成29年度(2017)～令和8年度(2026)</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>今年度末満了（2027年3月）</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr"/>
       <c r="I27" s="5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>10年経過（5年超）</t>
-        </is>
-      </c>
-      <c r="K27" s="5" t="inlineStr">
-        <is>
-          <t>今年度末満了／5年超経過</t>
-        </is>
-      </c>
-      <c r="L27" s="9" t="inlineStr">
-        <is>
-          <t>A：改訂着手が必要</t>
+          <t>2年経過</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr"/>
+      <c r="L27" s="7" t="inlineStr">
+        <is>
+          <t>C：翌年度以降に検討</t>
         </is>
       </c>
       <c r="M27" s="5" t="inlineStr">
@@ -2670,65 +2671,65 @@
       </c>
       <c r="N27" s="6" t="inlineStr">
         <is>
-          <t>算定期間 平成29年度～令和8年度→R8年度末満了。下水道ビジョンはR4-R13</t>
+          <t>令和7年3月策定。総務省様式で水道・下水道・農集排の会計単位の経営戦略を公表</t>
         </is>
       </c>
       <c r="O27" s="6" t="inlineStr">
         <is>
-          <t>https://www.city.tsuruoka.lg.jp/kurashi/suido/gesuido/jigyo_keiei/suido0120170327.html</t>
+          <t>https://www.city.akita.lg.jp/suido/jigyo-shokai/1045766.html</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>福島県</t>
+          <t>山形県</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>いわき市</t>
+          <t>山形市</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>下水道（公共）</t>
+          <t>上下水道（水道・下水道一体）</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>いわき市下水道事業経営戦略</t>
+          <t>山形市上下水道事業基本計画 NEXTビジョン2023</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>平成30年度(2018)</t>
-        </is>
-      </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>令和5年度(2023)</t>
-        </is>
-      </c>
+          <t>令和4年度(2022)</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr"/>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>令和1年度(2019)～令和10年度(2028)</t>
+          <t>令和5年度(2023)～令和14年度(2032)</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>満了は令和10年度(2028)末</t>
+          <t>満了は令和14年度(2032)末</t>
         </is>
       </c>
       <c r="I28" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>3年経過</t>
-        </is>
-      </c>
-      <c r="K28" s="5" t="inlineStr"/>
+          <t>4年経過（翌年度に5年）</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>翌年度5年</t>
+        </is>
+      </c>
       <c r="L28" s="7" t="inlineStr">
         <is>
           <t>C：翌年度以降に検討</t>
@@ -2741,24 +2742,24 @@
       </c>
       <c r="N28" s="6" t="inlineStr">
         <is>
-          <t>平成31年3月策定、R1-R10。前後期5年で区分しR3年度以降に中間見直し（R6.2公表）</t>
+          <t>計画期間 令和5年度～令和14年度</t>
         </is>
       </c>
       <c r="O28" s="6" t="inlineStr">
         <is>
-          <t>https://www.city.iwaki.lg.jp/www/contents/1707351258492/index.html</t>
+          <t>https://suidou.yamagata.yamagata.jp/soshiki/3/105858.html</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>福島県</t>
+          <t>山形県</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>会津若松市</t>
+          <t>鶴岡市</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -2768,52 +2769,56 @@
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>会津若松市下水道事業経営戦略</t>
+          <t>鶴岡市下水道事業経営戦略</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>令和6年度(2024)</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>令和6年度(2024)</t>
-        </is>
-      </c>
+          <t>平成28年度(2016)</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr"/>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H29" s="5" t="inlineStr"/>
+          <t>平成29年度(2017)～令和8年度(2026)</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>今年度末満了（2027年3月）</t>
+        </is>
+      </c>
       <c r="I29" s="5" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>2年経過</t>
-        </is>
-      </c>
-      <c r="K29" s="5" t="inlineStr"/>
-      <c r="L29" s="7" t="inlineStr">
-        <is>
-          <t>C：翌年度以降に検討</t>
+          <t>10年経過（5年超）</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>今年度末満了／5年超経過</t>
+        </is>
+      </c>
+      <c r="L29" s="9" t="inlineStr">
+        <is>
+          <t>A：改訂着手が必要</t>
         </is>
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="N29" s="6" t="inlineStr">
         <is>
-          <t>H28年度に旧特別会計ごとに策定→R2年度の法適用に伴い3会計を統合し策定（R6.11公表）</t>
+          <t>算定期間 平成29年度～令和8年度→R8年度末満了。下水道ビジョンはR4-R13</t>
         </is>
       </c>
       <c r="O29" s="6" t="inlineStr">
         <is>
-          <t>https://www.city.aizuwakamatsu.fukushima.jp/docs/2024112600048/</t>
+          <t>https://www.city.tsuruoka.lg.jp/kurashi/suido/gesuido/jigyo_keiei/suido0120170327.html</t>
         </is>
       </c>
     </row>
@@ -2825,55 +2830,51 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>会津若松市</t>
+          <t>いわき市</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>水道</t>
+          <t>下水道（公共）</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>会津若松市水道事業ビジョン2026／水道事業経営戦略</t>
+          <t>いわき市下水道事業経営戦略</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>平成28年度(2016)</t>
+          <t>平成30年度(2018)</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>令和7年度(2025)</t>
+          <t>令和5年度(2023)</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>～令和7年度(2025)</t>
+          <t>令和1年度(2019)～令和10年度(2028)</t>
         </is>
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>既に満了（令和7年度(2025)末）</t>
+          <t>満了は令和10年度(2028)末</t>
         </is>
       </c>
       <c r="I30" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>1年経過</t>
-        </is>
-      </c>
-      <c r="K30" s="5" t="inlineStr">
-        <is>
-          <t>期間満了済</t>
-        </is>
-      </c>
-      <c r="L30" s="9" t="inlineStr">
-        <is>
-          <t>A：改訂着手が必要</t>
+          <t>3年経過</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="inlineStr"/>
+      <c r="L30" s="7" t="inlineStr">
+        <is>
+          <t>C：翌年度以降に検討</t>
         </is>
       </c>
       <c r="M30" s="5" t="inlineStr">
@@ -2883,12 +2884,12 @@
       </c>
       <c r="N30" s="6" t="inlineStr">
         <is>
-          <t>H28年度策定分がR7年度で目標年度到達→令和8年1月にビジョン2026・新経営戦略（案）のパブコメ実施＝改定作業中</t>
+          <t>平成31年3月策定、R1-R10。前後期5年で区分しR3年度以降に中間見直し（R6.2公表）</t>
         </is>
       </c>
       <c r="O30" s="6" t="inlineStr">
         <is>
-          <t>https://www.city.aizuwakamatsu.fukushima.jp/docs/2026010600014/</t>
+          <t>https://www.city.iwaki.lg.jp/www/contents/1707351258492/index.html</t>
         </is>
       </c>
     </row>
@@ -2905,40 +2906,36 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>簡易水道</t>
+          <t>下水道</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>会津若松市簡易水道事業経営戦略</t>
+          <t>会津若松市下水道事業経営戦略</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>令和2年度(2020)</t>
+          <t>令和6年度(2024)</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>令和7年度(2025)</t>
+          <t>令和6年度(2024)</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>令和3年度(2021)～令和12年度(2030)</t>
-        </is>
-      </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>満了は令和12年度(2030)末</t>
-        </is>
-      </c>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr"/>
       <c r="I31" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>1年経過</t>
+          <t>2年経過</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr"/>
@@ -2949,17 +2946,17 @@
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="N31" s="6" t="inlineStr">
         <is>
-          <t>令和3年3月策定（R3-R12）、令和7年11月改定</t>
+          <t>H28年度に旧特別会計ごとに策定→R2年度の法適用に伴い3会計を統合し策定（R6.11公表）</t>
         </is>
       </c>
       <c r="O31" s="6" t="inlineStr">
         <is>
-          <t>https://www.city.aizuwakamatsu.fukushima.jp/docs/2021031900044/file_contents/kansui-senryaku-R7kaitei.pdf</t>
+          <t>https://www.city.aizuwakamatsu.fukushima.jp/docs/2024112600048/</t>
         </is>
       </c>
     </row>
@@ -2971,28 +2968,32 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>福島市</t>
+          <t>会津若松市</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>下水道</t>
+          <t>水道</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>福島市下水道ビジョン（中期計画）</t>
+          <t>会津若松市水道事業ビジョン2026／水道事業経営戦略</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>平成27年度(2015)</t>
-        </is>
-      </c>
-      <c r="F32" s="5" t="inlineStr"/>
+          <t>平成28年度(2016)</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>令和7年度(2025)</t>
+        </is>
+      </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>平成28年度(2016)～令和7年度(2025)</t>
+          <t>～令和7年度(2025)</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
@@ -3001,16 +3002,16 @@
         </is>
       </c>
       <c r="I32" s="5" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>11年経過（5年超）</t>
+          <t>1年経過</t>
         </is>
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>期間満了済／5年超経過</t>
+          <t>期間満了済</t>
         </is>
       </c>
       <c r="L32" s="9" t="inlineStr">
@@ -3020,17 +3021,17 @@
       </c>
       <c r="M32" s="5" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="N32" s="6" t="inlineStr">
         <is>
-          <t>平成28年度～令和7年度→R7年度末で満了済。経営戦略の改定状況は要確認</t>
+          <t>H28年度策定分がR7年度で目標年度到達→令和8年1月にビジョン2026・新経営戦略（案）のパブコメ実施＝改定作業中</t>
         </is>
       </c>
       <c r="O32" s="6" t="inlineStr">
         <is>
-          <t>https://www.city.fukushima.fukushima.jp/material/files/group/67/7fukushimasinogesuidou.pdf</t>
+          <t>https://www.city.aizuwakamatsu.fukushima.jp/docs/2026010600014/</t>
         </is>
       </c>
     </row>
@@ -3042,48 +3043,66 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>福島市</t>
+          <t>会津若松市</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>水道</t>
+          <t>簡易水道</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>ふくしま水道事業ビジョン</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr"/>
-      <c r="F33" s="5" t="inlineStr"/>
+          <t>会津若松市簡易水道事業経営戦略</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>令和2年度(2020)</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>令和7年度(2025)</t>
+        </is>
+      </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="H33" s="5" t="inlineStr"/>
-      <c r="I33" s="5" t="inlineStr"/>
-      <c r="J33" s="5" t="inlineStr"/>
+          <t>令和3年度(2021)～令和12年度(2030)</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>満了は令和12年度(2030)末</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>1年経過</t>
+        </is>
+      </c>
       <c r="K33" s="5" t="inlineStr"/>
-      <c r="L33" s="8" t="inlineStr">
-        <is>
-          <t>－：情報未確認</t>
+      <c r="L33" s="7" t="inlineStr">
+        <is>
+          <t>C：翌年度以降に検討</t>
         </is>
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>低</t>
+          <t>高</t>
         </is>
       </c>
       <c r="N33" s="6" t="inlineStr">
         <is>
-          <t>公表済。計画期間の年度は要確認</t>
+          <t>令和3年3月策定（R3-R12）、令和7年11月改定</t>
         </is>
       </c>
       <c r="O33" s="6" t="inlineStr">
         <is>
-          <t>https://www.city.fukushima.fukushima.jp/suidou/</t>
+          <t>https://www.city.aizuwakamatsu.fukushima.jp/docs/2021031900044/file_contents/kansui-senryaku-R7kaitei.pdf</t>
         </is>
       </c>
     </row>
@@ -3095,64 +3114,188 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
+          <t>福島市</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>下水道</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>福島市下水道ビジョン（中期計画）</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>平成27年度(2015)</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr"/>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>平成28年度(2016)～令和7年度(2025)</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>既に満了（令和7年度(2025)末）</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>11年経過（5年超）</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="inlineStr">
+        <is>
+          <t>期間満了済／5年超経過</t>
+        </is>
+      </c>
+      <c r="L34" s="9" t="inlineStr">
+        <is>
+          <t>A：改訂着手が必要</t>
+        </is>
+      </c>
+      <c r="M34" s="5" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="N34" s="6" t="inlineStr">
+        <is>
+          <t>平成28年度～令和7年度→R7年度末で満了済。経営戦略の改定状況は要確認</t>
+        </is>
+      </c>
+      <c r="O34" s="6" t="inlineStr">
+        <is>
+          <t>https://www.city.fukushima.fukushima.jp/material/files/group/67/7fukushimasinogesuidou.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>福島県</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>福島市</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>水道</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>ふくしま水道事業ビジョン</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr"/>
+      <c r="F35" s="5" t="inlineStr"/>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr"/>
+      <c r="I35" s="5" t="inlineStr"/>
+      <c r="J35" s="5" t="inlineStr"/>
+      <c r="K35" s="5" t="inlineStr"/>
+      <c r="L35" s="8" t="inlineStr">
+        <is>
+          <t>－：情報未確認</t>
+        </is>
+      </c>
+      <c r="M35" s="5" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="N35" s="6" t="inlineStr">
+        <is>
+          <t>検索では計画期間を特定できず。水道局への個別確認が必要</t>
+        </is>
+      </c>
+      <c r="O35" s="6" t="inlineStr">
+        <is>
+          <t>https://www.city.fukushima.fukushima.jp/suidou/</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>福島県</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
           <t>郡山市</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>上下水道（水道・下水道一体）</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr">
+      <c r="D36" s="6" t="inlineStr">
         <is>
           <t>郡山市上下水道ビジョン2.0～郡山市上下水道事業経営戦略～</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>令和1年度(2019)</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>令和6年度(2024)</t>
         </is>
       </c>
-      <c r="G34" s="5" t="inlineStr">
+      <c r="G36" s="5" t="inlineStr">
         <is>
           <t>令和2年度(2020)～令和11年度(2029)</t>
         </is>
       </c>
-      <c r="H34" s="5" t="inlineStr">
+      <c r="H36" s="5" t="inlineStr">
         <is>
           <t>満了は令和11年度(2029)末</t>
         </is>
       </c>
-      <c r="I34" s="5" t="n">
+      <c r="I36" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="J34" s="5" t="inlineStr">
+      <c r="J36" s="5" t="inlineStr">
         <is>
           <t>2年経過</t>
         </is>
       </c>
-      <c r="K34" s="5" t="inlineStr"/>
-      <c r="L34" s="7" t="inlineStr">
+      <c r="K36" s="5" t="inlineStr"/>
+      <c r="L36" s="7" t="inlineStr">
         <is>
           <t>C：翌年度以降に検討</t>
         </is>
       </c>
-      <c r="M34" s="5" t="inlineStr">
+      <c r="M36" s="5" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="N34" s="6" t="inlineStr">
+      <c r="N36" s="6" t="inlineStr">
         <is>
           <t>2020(R2)-2029(R11)。令和7年3月に中間改定</t>
         </is>
       </c>
-      <c r="O34" s="6" t="inlineStr">
+      <c r="O36" s="6" t="inlineStr">
         <is>
           <t>https://www.city.koriyama.lg.jp/site/jougesuidou/5629.html</t>
         </is>
@@ -3175,7 +3318,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3287,17 +3430,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>北上市</t>
+          <t>一関市</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>下水道（公共・農業集落排水）</t>
+          <t>下水道</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>北上市下水道事業経営戦略</t>
+          <t>一関市下水道事業経営戦略</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -3305,7 +3448,11 @@
           <t>平成28年度(2016)</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr"/>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>令和4年度(2022)</t>
+        </is>
+      </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
           <t>平成29年度(2017)～令和8年度(2026)</t>
@@ -3317,16 +3464,16 @@
         </is>
       </c>
       <c r="I3" s="5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>10年経過（5年超）</t>
+          <t>4年経過（翌年度に5年）</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>今年度末満了／5年超経過</t>
+          <t>今年度末満了／翌年度5年</t>
         </is>
       </c>
       <c r="L3" s="9" t="inlineStr">
@@ -3336,17 +3483,17 @@
       </c>
       <c r="M3" s="5" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="N3" s="6" t="inlineStr">
         <is>
-          <t>平成29年度～令和8年度の10年間→R8年度末満了</t>
+          <t>平成29年3月策定。令和5年3月版PDFあり（改定）。汚水処理施設整備計画はH29-H38（＝R8年度）。改定後の計画期間は要電話確認</t>
         </is>
       </c>
       <c r="O3" s="6" t="inlineStr">
         <is>
-          <t>https://www.city.kitakami.iwate.jp/life/kurashi_tetsuduki/jo_gesuido/gesuido/10131.html</t>
+          <t>https://www.city.ichinoseki.iwate.jp/uploads/contents/archive_0000000308_00/20230331-110723.pdf</t>
         </is>
       </c>
     </row>
@@ -3363,23 +3510,23 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>下水道（特定公共下水道）</t>
+          <t>下水道（公共・農業集落排水）</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>北上市特定公共下水道事業経営戦略</t>
+          <t>北上市下水道事業経営戦略</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>平成29年度(2017)</t>
+          <t>平成28年度(2016)</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr"/>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>平成30年度(2018)～令和8年度(2026)</t>
+          <t>平成29年度(2017)～令和8年度(2026)</t>
         </is>
       </c>
       <c r="H4" s="5" t="inlineStr">
@@ -3388,11 +3535,11 @@
         </is>
       </c>
       <c r="I4" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>9年経過（5年超）</t>
+          <t>10年経過（5年超）</t>
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr">
@@ -3412,7 +3559,7 @@
       </c>
       <c r="N4" s="6" t="inlineStr">
         <is>
-          <t>平成30年度～令和8年度の9年間→R8年度末満了</t>
+          <t>平成29年度～令和8年度の10年間→R8年度末満了</t>
         </is>
       </c>
       <c r="O4" s="6" t="inlineStr">
@@ -3424,69 +3571,140 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>山形県</t>
+          <t>岩手県</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>鶴岡市</t>
+          <t>北上市</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>下水道</t>
+          <t>下水道（特定公共下水道）</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>鶴岡市下水道事業経営戦略</t>
+          <t>北上市特定公共下水道事業経営戦略</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>平成28年度(2016)</t>
+          <t>平成29年度(2017)</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr"/>
       <c r="G5" s="5" t="inlineStr">
         <is>
+          <t>平成30年度(2018)～令和8年度(2026)</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>今年度末満了（2027年3月）</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>9年経過（5年超）</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>今年度末満了／5年超経過</t>
+        </is>
+      </c>
+      <c r="L5" s="9" t="inlineStr">
+        <is>
+          <t>A：改訂着手が必要</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="N5" s="6" t="inlineStr">
+        <is>
+          <t>平成30年度～令和8年度の9年間→R8年度末満了</t>
+        </is>
+      </c>
+      <c r="O5" s="6" t="inlineStr">
+        <is>
+          <t>https://www.city.kitakami.iwate.jp/life/kurashi_tetsuduki/jo_gesuido/gesuido/10131.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>山形県</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>鶴岡市</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>下水道</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>鶴岡市下水道事業経営戦略</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>平成28年度(2016)</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr"/>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
           <t>平成29年度(2017)～令和8年度(2026)</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>今年度末満了（2027年3月）</t>
         </is>
       </c>
-      <c r="I5" s="5" t="n">
+      <c r="I6" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>10年経過（5年超）</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="K6" s="5" t="inlineStr">
         <is>
           <t>今年度末満了／5年超経過</t>
         </is>
       </c>
-      <c r="L5" s="9" t="inlineStr">
+      <c r="L6" s="9" t="inlineStr">
         <is>
           <t>A：改訂着手が必要</t>
         </is>
       </c>
-      <c r="M5" s="5" t="inlineStr">
+      <c r="M6" s="5" t="inlineStr">
         <is>
           <t>高</t>
         </is>
       </c>
-      <c r="N5" s="6" t="inlineStr">
+      <c r="N6" s="6" t="inlineStr">
         <is>
           <t>算定期間 平成29年度～令和8年度→R8年度末満了。下水道ビジョンはR4-R13</t>
         </is>
       </c>
-      <c r="O5" s="6" t="inlineStr">
+      <c r="O6" s="6" t="inlineStr">
         <is>
           <t>https://www.city.tsuruoka.lg.jp/kurashi/suido/gesuido/jigyo_keiei/suido0120170327.html</t>
         </is>
@@ -5684,20 +5902,25 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>－</t>
+          <t>水道：令和8年度(2026)～令和17年度(2035)／満了は令和17年度(2035)末</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>水道・下水道：不明／－</t>
-        </is>
-      </c>
-      <c r="E6" s="13" t="inlineStr">
-        <is>
-          <t>－：情報未確認</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr"/>
+          <t>水道・下水道：不明／－
+下水道：平成29年度(2017)～令和8年度(2026)／今年度末満了／翌年度5年</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>A：改訂着手が必要</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>今年度末満了／翌年度5年</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -5873,7 +6096,7 @@
           <t>下水道：令和7年度(2025)～令和16年度(2034)／満了は令和16年度(2034)末</t>
         </is>
       </c>
-      <c r="E12" s="14" t="inlineStr">
+      <c r="E12" s="13" t="inlineStr">
         <is>
           <t>B：来年度改訂の対象</t>
         </is>
@@ -5938,7 +6161,7 @@
           <t>下水道：令和4年度(2022)～令和13年度(2031)／5年経過</t>
         </is>
       </c>
-      <c r="E14" s="14" t="inlineStr">
+      <c r="E14" s="13" t="inlineStr">
         <is>
           <t>B：来年度改訂の対象</t>
         </is>
@@ -6176,7 +6399,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6430,17 +6653,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>北上市</t>
+          <t>一関市</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>下水道（公共・農業集落排水）</t>
+          <t>下水道</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>北上市下水道事業経営戦略</t>
+          <t>一関市下水道事業経営戦略</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -6448,7 +6671,11 @@
           <t>平成28年度(2016)</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr"/>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>令和4年度(2022)</t>
+        </is>
+      </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
           <t>平成29年度(2017)～令和8年度(2026)</t>
@@ -6460,16 +6687,16 @@
         </is>
       </c>
       <c r="I5" s="5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>10年経過（5年超）</t>
+          <t>4年経過（翌年度に5年）</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>今年度末満了／5年超経過</t>
+          <t>今年度末満了／翌年度5年</t>
         </is>
       </c>
       <c r="L5" s="9" t="inlineStr">
@@ -6479,17 +6706,17 @@
       </c>
       <c r="M5" s="5" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="N5" s="6" t="inlineStr">
         <is>
-          <t>平成29年度～令和8年度の10年間→R8年度末満了</t>
+          <t>平成29年3月策定。令和5年3月版PDFあり（改定）。汚水処理施設整備計画はH29-H38（＝R8年度）。改定後の計画期間は要電話確認</t>
         </is>
       </c>
       <c r="O5" s="6" t="inlineStr">
         <is>
-          <t>https://www.city.kitakami.iwate.jp/life/kurashi_tetsuduki/jo_gesuido/gesuido/10131.html</t>
+          <t>https://www.city.ichinoseki.iwate.jp/uploads/contents/archive_0000000308_00/20230331-110723.pdf</t>
         </is>
       </c>
     </row>
@@ -6506,23 +6733,23 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>下水道（特定公共下水道）</t>
+          <t>下水道（公共・農業集落排水）</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>北上市特定公共下水道事業経営戦略</t>
+          <t>北上市下水道事業経営戦略</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>平成29年度(2017)</t>
+          <t>平成28年度(2016)</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr"/>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>平成30年度(2018)～令和8年度(2026)</t>
+          <t>平成29年度(2017)～令和8年度(2026)</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
@@ -6531,11 +6758,11 @@
         </is>
       </c>
       <c r="I6" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>9年経過（5年超）</t>
+          <t>10年経過（5年超）</t>
         </is>
       </c>
       <c r="K6" s="5" t="inlineStr">
@@ -6555,7 +6782,7 @@
       </c>
       <c r="N6" s="6" t="inlineStr">
         <is>
-          <t>平成30年度～令和8年度の9年間→R8年度末満了</t>
+          <t>平成29年度～令和8年度の10年間→R8年度末満了</t>
         </is>
       </c>
       <c r="O6" s="6" t="inlineStr">
@@ -6572,50 +6799,46 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>盛岡市</t>
+          <t>北上市</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>下水道</t>
+          <t>下水道（特定公共下水道）</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>盛岡市下水道事業中長期経営計画</t>
+          <t>北上市特定公共下水道事業経営戦略</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>平成26年度(2014)</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>平成28年度(2016)</t>
-        </is>
-      </c>
+          <t>平成29年度(2017)</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr"/>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>平成27年度(2015)～令和6年度(2024)</t>
+          <t>平成30年度(2018)～令和8年度(2026)</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>既に満了（令和6年度(2024)末）</t>
+          <t>今年度末満了（2027年3月）</t>
         </is>
       </c>
       <c r="I7" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>10年経過（5年超）</t>
+          <t>9年経過（5年超）</t>
         </is>
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>期間満了済／5年超経過</t>
+          <t>今年度末満了／5年超経過</t>
         </is>
       </c>
       <c r="L7" s="9" t="inlineStr">
@@ -6625,29 +6848,29 @@
       </c>
       <c r="M7" s="5" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="N7" s="6" t="inlineStr">
         <is>
-          <t>平成27年3月策定（H27-H36＝令和6年度）、平成29年3月改訂→R6年度末で満了。別途「下水道事業中期経営計画」あり、最新版は要確認</t>
+          <t>平成30年度～令和8年度の9年間→R8年度末満了</t>
         </is>
       </c>
       <c r="O7" s="6" t="inlineStr">
         <is>
-          <t>https://www.morioka-water.jp/about/ge_plan_27-36.html</t>
+          <t>https://www.city.kitakami.iwate.jp/life/kurashi_tetsuduki/jo_gesuido/gesuido/10131.html</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>宮城県</t>
+          <t>岩手県</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>仙台市</t>
+          <t>盛岡市</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6657,31 +6880,35 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>仙台市下水道事業中期経営計画（後期）</t>
+          <t>盛岡市下水道事業中長期経営計画</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>令和2年度(2020)</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr"/>
+          <t>平成26年度(2014)</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>平成28年度(2016)</t>
+        </is>
+      </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>令和3年度(2021)～令和7年度(2025)</t>
+          <t>平成27年度(2015)～令和6年度(2024)</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>既に満了（令和7年度(2025)末）</t>
+          <t>既に満了（令和6年度(2024)末）</t>
         </is>
       </c>
       <c r="I8" s="5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>6年経過（5年超）</t>
+          <t>10年経過（5年超）</t>
         </is>
       </c>
       <c r="K8" s="5" t="inlineStr">
@@ -6696,17 +6923,17 @@
       </c>
       <c r="M8" s="5" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="N8" s="6" t="inlineStr">
         <is>
-          <t>令和3年3月策定、R3-R7の5年間→R7年度末で満了済。次期計画の策定状況は要確認</t>
+          <t>平成27年3月策定（H27-H36＝令和6年度）、平成29年3月改訂→R6年度末で満了。別途「下水道事業中期経営計画」あり、最新版は要確認</t>
         </is>
       </c>
       <c r="O8" s="6" t="inlineStr">
         <is>
-          <t>https://www.city.sendai.jp/keesenryaku/kurashi/machi/lifeline/gesuido/gesuido/gaiyo/kee.html</t>
+          <t>https://www.morioka-water.jp/about/ge_plan_27-36.html</t>
         </is>
       </c>
     </row>
@@ -6718,7 +6945,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>石巻市</t>
+          <t>仙台市</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6728,22 +6955,18 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>石巻市下水道事業経営戦略（改定版）</t>
+          <t>仙台市下水道事業中期経営計画（後期）</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>平成27年度(2015)</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>令和5年度(2023)</t>
-        </is>
-      </c>
+          <t>令和2年度(2020)</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr"/>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>平成28年度(2016)～令和7年度(2025)</t>
+          <t>令和3年度(2021)～令和7年度(2025)</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
@@ -6752,16 +6975,16 @@
         </is>
       </c>
       <c r="I9" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>3年経過</t>
+          <t>6年経過（5年超）</t>
         </is>
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>期間満了済</t>
+          <t>期間満了済／5年超経過</t>
         </is>
       </c>
       <c r="L9" s="9" t="inlineStr">
@@ -6771,29 +6994,29 @@
       </c>
       <c r="M9" s="5" t="inlineStr">
         <is>
-          <t>中</t>
+          <t>高</t>
         </is>
       </c>
       <c r="N9" s="6" t="inlineStr">
         <is>
-          <t>H28.3策定（H28-R7）→R6.2～3にパブコメを経て改定。改定後の計画期間は要確認</t>
+          <t>令和3年3月策定、R3-R7の5年間→R7年度末で満了済。次期計画の策定状況は要確認</t>
         </is>
       </c>
       <c r="O9" s="6" t="inlineStr">
         <is>
-          <t>https://www.city.ishinomaki.lg.jp/cont/10505200/20240312085340.html</t>
+          <t>https://www.city.sendai.jp/keesenryaku/kurashi/machi/lifeline/gesuido/gesuido/gaiyo/kee.html</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>山形県</t>
+          <t>宮城県</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>鶴岡市</t>
+          <t>石巻市</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -6803,36 +7026,40 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>鶴岡市下水道事業経営戦略</t>
+          <t>石巻市下水道事業経営戦略（改定版）</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>平成28年度(2016)</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr"/>
+          <t>平成27年度(2015)</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>令和5年度(2023)</t>
+        </is>
+      </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>平成29年度(2017)～令和8年度(2026)</t>
+          <t>平成28年度(2016)～令和7年度(2025)</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>今年度末満了（2027年3月）</t>
+          <t>既に満了（令和7年度(2025)末）</t>
         </is>
       </c>
       <c r="I10" s="5" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>10年経過（5年超）</t>
+          <t>3年経過</t>
         </is>
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>今年度末満了／5年超経過</t>
+          <t>期間満了済</t>
         </is>
       </c>
       <c r="L10" s="9" t="inlineStr">
@@ -6842,39 +7069,39 @@
       </c>
       <c r="M10" s="5" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>中</t>
         </is>
       </c>
       <c r="N10" s="6" t="inlineStr">
         <is>
-          <t>算定期間 平成29年度～令和8年度→R8年度末満了。下水道ビジョンはR4-R13</t>
+          <t>H28.3策定（H28-R7）→R6.2～3にパブコメを経て改定。改定後の計画期間は要確認</t>
         </is>
       </c>
       <c r="O10" s="6" t="inlineStr">
         <is>
-          <t>https://www.city.tsuruoka.lg.jp/kurashi/suido/gesuido/jigyo_keiei/suido0120170327.html</t>
+          <t>https://www.city.ishinomaki.lg.jp/cont/10505200/20240312085340.html</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>福島県</t>
+          <t>山形県</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>会津若松市</t>
+          <t>鶴岡市</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>水道</t>
+          <t>下水道</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>会津若松市水道事業ビジョン2026／水道事業経営戦略</t>
+          <t>鶴岡市下水道事業経営戦略</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -6882,32 +7109,28 @@
           <t>平成28年度(2016)</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>令和7年度(2025)</t>
-        </is>
-      </c>
+      <c r="F11" s="5" t="inlineStr"/>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>～令和7年度(2025)</t>
+          <t>平成29年度(2017)～令和8年度(2026)</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>既に満了（令和7年度(2025)末）</t>
+          <t>今年度末満了（2027年3月）</t>
         </is>
       </c>
       <c r="I11" s="5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>1年経過</t>
+          <t>10年経過（5年超）</t>
         </is>
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>期間満了済</t>
+          <t>今年度末満了／5年超経過</t>
         </is>
       </c>
       <c r="L11" s="9" t="inlineStr">
@@ -6922,12 +7145,12 @@
       </c>
       <c r="N11" s="6" t="inlineStr">
         <is>
-          <t>H28年度策定分がR7年度で目標年度到達→令和8年1月にビジョン2026・新経営戦略（案）のパブコメ実施＝改定作業中</t>
+          <t>算定期間 平成29年度～令和8年度→R8年度末満了。下水道ビジョンはR4-R13</t>
         </is>
       </c>
       <c r="O11" s="6" t="inlineStr">
         <is>
-          <t>https://www.city.aizuwakamatsu.fukushima.jp/docs/2026010600014/</t>
+          <t>https://www.city.tsuruoka.lg.jp/kurashi/suido/gesuido/jigyo_keiei/suido0120170327.html</t>
         </is>
       </c>
     </row>
@@ -6939,64 +7162,139 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
+          <t>会津若松市</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>水道</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>会津若松市水道事業ビジョン2026／水道事業経営戦略</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>平成28年度(2016)</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>令和7年度(2025)</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>～令和7年度(2025)</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>既に満了（令和7年度(2025)末）</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>1年経過</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>期間満了済</t>
+        </is>
+      </c>
+      <c r="L12" s="9" t="inlineStr">
+        <is>
+          <t>A：改訂着手が必要</t>
+        </is>
+      </c>
+      <c r="M12" s="5" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="N12" s="6" t="inlineStr">
+        <is>
+          <t>H28年度策定分がR7年度で目標年度到達→令和8年1月にビジョン2026・新経営戦略（案）のパブコメ実施＝改定作業中</t>
+        </is>
+      </c>
+      <c r="O12" s="6" t="inlineStr">
+        <is>
+          <t>https://www.city.aizuwakamatsu.fukushima.jp/docs/2026010600014/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>福島県</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
           <t>福島市</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>下水道</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>福島市下水道ビジョン（中期計画）</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>平成27年度(2015)</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr"/>
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>平成28年度(2016)～令和7年度(2025)</t>
         </is>
       </c>
-      <c r="H12" s="5" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>既に満了（令和7年度(2025)末）</t>
         </is>
       </c>
-      <c r="I12" s="5" t="n">
+      <c r="I13" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="J12" s="5" t="inlineStr">
+      <c r="J13" s="5" t="inlineStr">
         <is>
           <t>11年経過（5年超）</t>
         </is>
       </c>
-      <c r="K12" s="5" t="inlineStr">
+      <c r="K13" s="5" t="inlineStr">
         <is>
           <t>期間満了済／5年超経過</t>
         </is>
       </c>
-      <c r="L12" s="9" t="inlineStr">
+      <c r="L13" s="9" t="inlineStr">
         <is>
           <t>A：改訂着手が必要</t>
         </is>
       </c>
-      <c r="M12" s="5" t="inlineStr">
+      <c r="M13" s="5" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="N12" s="6" t="inlineStr">
+      <c r="N13" s="6" t="inlineStr">
         <is>
           <t>平成28年度～令和7年度→R7年度末で満了済。経営戦略の改定状況は要確認</t>
         </is>
       </c>
-      <c r="O12" s="6" t="inlineStr">
+      <c r="O13" s="6" t="inlineStr">
         <is>
           <t>https://www.city.fukushima.fukushima.jp/material/files/group/67/7fukushimasinogesuidou.pdf</t>
         </is>
@@ -7167,12 +7465,12 @@
       </c>
       <c r="N3" s="6" t="inlineStr">
         <is>
-          <t>八戸市の水道は八戸圏域水道企業団が運営。計画期間は要確認</t>
+          <t>検索では計画期間を特定できず。企業団経営企画課への個別確認が必要（八戸市・三戸町等の構成団体）</t>
         </is>
       </c>
       <c r="O3" s="6" t="inlineStr">
         <is>
-          <t>https://www.city.hachinohe.aomori.jp/soshikikarasagasu/gesuidogyomuka/2621.html</t>
+          <t>https://www.water-supply.hachinohe.aomori.jp/</t>
         </is>
       </c>
     </row>
@@ -7273,7 +7571,7 @@
       </c>
       <c r="N5" s="6" t="inlineStr">
         <is>
-          <t>公表済。計画期間の年度は要確認</t>
+          <t>検索では計画期間を特定できず。水道局への個別確認が必要</t>
         </is>
       </c>
       <c r="O5" s="6" t="inlineStr">
